--- a/exports/trend_1d/SRF_full_report.xlsx
+++ b/exports/trend_1d/SRF_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.59</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H2" t="n">
-        <v>200.85</v>
+        <v>192</v>
       </c>
       <c r="I2" t="n">
         <v>192.3659129790364</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>9.4</v>
+        <v>4.58</v>
       </c>
       <c r="L2" t="n">
         <v>4.63</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>18.25</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H3" t="n">
-        <v>202.1</v>
+        <v>220.2</v>
       </c>
       <c r="I3" t="n">
         <v>213.8929654087556</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.26</v>
+        <v>-14.69</v>
       </c>
       <c r="L3" t="n">
-        <v>9.77</v>
+        <v>18.52</v>
       </c>
       <c r="M3" t="n">
         <v>1.95</v>
       </c>
       <c r="N3" t="n">
-        <v>4.45</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>-4.41</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.53</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H4" t="n">
-        <v>278.1</v>
+        <v>262.95</v>
       </c>
       <c r="I4" t="n">
         <v>266.4614345951337</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K4" t="n">
-        <v>26.29</v>
+        <v>19.41</v>
       </c>
       <c r="L4" t="n">
         <v>8.99</v>
@@ -669,7 +716,7 @@
         <v>2.37</v>
       </c>
       <c r="N4" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="O4" t="n">
         <v>8.960000000000001</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.08</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42292</v>
+        <v>42293</v>
       </c>
       <c r="H5" t="n">
-        <v>253.2</v>
+        <v>260.55</v>
       </c>
       <c r="I5" t="n">
         <v>255.8150769552311</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.71</v>
+        <v>0.91</v>
       </c>
       <c r="L5" t="n">
         <v>5.72</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>12</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42319</v>
+        <v>42321</v>
       </c>
       <c r="H6" t="n">
-        <v>254.25</v>
+        <v>244.8</v>
       </c>
       <c r="I6" t="n">
         <v>246.5364103123701</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.42</v>
+        <v>-6.04</v>
       </c>
       <c r="L6" t="n">
-        <v>5.49</v>
+        <v>11.21</v>
       </c>
       <c r="M6" t="n">
         <v>3.64</v>
       </c>
       <c r="N6" t="n">
-        <v>2.69</v>
+        <v>3.72</v>
       </c>
       <c r="O6" t="n">
         <v>2.9</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.96</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42373</v>
+        <v>42374</v>
       </c>
       <c r="H7" t="n">
-        <v>249.4</v>
+        <v>256.45</v>
       </c>
       <c r="I7" t="n">
         <v>255.9109301727494</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.88</v>
+        <v>-4.76</v>
       </c>
       <c r="L7" t="n">
         <v>5.78</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>9.52</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H8" t="n">
-        <v>242.65</v>
+        <v>228.45</v>
       </c>
       <c r="I8" t="n">
         <v>239.3417967567464</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.38</v>
+        <v>-10.92</v>
       </c>
       <c r="L8" t="n">
-        <v>6.08</v>
+        <v>11.7</v>
       </c>
       <c r="M8" t="n">
         <v>2.81</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>5.85</v>
       </c>
       <c r="O8" t="n">
         <v>2.83</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>16.62</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42432</v>
+        <v>42433</v>
       </c>
       <c r="H9" t="n">
-        <v>229.6</v>
+        <v>241.5</v>
       </c>
       <c r="I9" t="n">
         <v>236.1782497652555</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5</v>
+        <v>-5.71</v>
       </c>
       <c r="L9" t="n">
         <v>7.31</v>
@@ -954,7 +1061,7 @@
         <v>1.36</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>5.18</v>
       </c>
       <c r="O9" t="n">
         <v>-5.85</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.76</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42502</v>
+        <v>42503</v>
       </c>
       <c r="H10" t="n">
-        <v>277.45</v>
+        <v>252.25</v>
       </c>
       <c r="I10" t="n">
         <v>259.4837236914942</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K10" t="n">
-        <v>14.89</v>
+        <v>4.45</v>
       </c>
       <c r="L10" t="n">
         <v>4.1</v>
@@ -1011,7 +1130,7 @@
         <v>2.41</v>
       </c>
       <c r="N10" t="n">
-        <v>3.66</v>
+        <v>9.08</v>
       </c>
       <c r="O10" t="n">
         <v>5.18</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>17.62</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42562</v>
+        <v>42563</v>
       </c>
       <c r="H11" t="n">
-        <v>263.3</v>
+        <v>270.7</v>
       </c>
       <c r="I11" t="n">
         <v>267.24629115825</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.38</v>
+        <v>-7.31</v>
       </c>
       <c r="L11" t="n">
         <v>8.539999999999999</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42633</v>
+        <v>42634</v>
       </c>
       <c r="H12" t="n">
-        <v>325.3</v>
+        <v>321.9</v>
       </c>
       <c r="I12" t="n">
         <v>322.8752643145608</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K12" t="n">
-        <v>20.17</v>
+        <v>18.91</v>
       </c>
       <c r="L12" t="n">
         <v>2.48</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>8.09</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42635</v>
+        <v>42636</v>
       </c>
       <c r="H13" t="n">
-        <v>324.85</v>
+        <v>357.55</v>
       </c>
       <c r="I13" t="n">
         <v>347.9312093532484</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.92</v>
+        <v>-11.07</v>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>11.84</v>
       </c>
       <c r="M13" t="n">
         <v>1.27</v>
       </c>
       <c r="N13" t="n">
-        <v>0.92</v>
+        <v>10.07</v>
       </c>
       <c r="O13" t="n">
         <v>-1.05</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>13.38</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42675</v>
+        <v>42676</v>
       </c>
       <c r="H14" t="n">
-        <v>362.7</v>
+        <v>347.05</v>
       </c>
       <c r="I14" t="n">
         <v>348.8679009540891</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K14" t="n">
-        <v>1.44</v>
+        <v>-2.94</v>
       </c>
       <c r="L14" t="n">
         <v>8.890000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.49</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>2.38</v>
+        <v>4.31</v>
       </c>
       <c r="O14" t="n">
         <v>10.07</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.5</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H15" t="n">
-        <v>315.2</v>
+        <v>330.4</v>
       </c>
       <c r="I15" t="n">
         <v>319.5253343434366</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K15" t="n">
-        <v>9.18</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>3.73</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42776</v>
+        <v>42779</v>
       </c>
       <c r="H16" t="n">
-        <v>350.4</v>
+        <v>320.15</v>
       </c>
       <c r="I16" t="n">
         <v>325.8825566316372</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K16" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L16" t="n">
         <v>6.05</v>
       </c>
-      <c r="L16" t="n">
-        <v>4.45</v>
-      </c>
       <c r="M16" t="n">
-        <v>0.06</v>
+        <v>2.11</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="O16" t="n">
         <v>4.82</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>13.6</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42837</v>
+        <v>42838</v>
       </c>
       <c r="H17" t="n">
-        <v>329.4</v>
+        <v>338.65</v>
       </c>
       <c r="I17" t="n">
         <v>335.8824373578801</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.89</v>
+        <v>-5.78</v>
       </c>
       <c r="L17" t="n">
         <v>8.539999999999999</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>7.87</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H18" t="n">
-        <v>341.4</v>
+        <v>322.4</v>
       </c>
       <c r="I18" t="n">
         <v>339.5752712827861</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8100000000000001</v>
+        <v>-4.8</v>
       </c>
       <c r="L18" t="n">
-        <v>3.5</v>
+        <v>5.85</v>
       </c>
       <c r="M18" t="n">
-        <v>0.67</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>3.24</v>
+        <v>5.57</v>
       </c>
       <c r="O18" t="n">
         <v>2.81</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>13.09</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42989</v>
+        <v>42990</v>
       </c>
       <c r="H19" t="n">
-        <v>310.05</v>
+        <v>319</v>
       </c>
       <c r="I19" t="n">
         <v>318.1782399365847</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K19" t="n">
-        <v>3.83</v>
+        <v>1.05</v>
       </c>
       <c r="L19" t="n">
         <v>5.61</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.98</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43124</v>
+        <v>43125</v>
       </c>
       <c r="H20" t="n">
-        <v>379.65</v>
+        <v>367.95</v>
       </c>
       <c r="I20" t="n">
         <v>373.6701530964214</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K20" t="n">
-        <v>19.01</v>
+        <v>15.34</v>
       </c>
       <c r="L20" t="n">
         <v>5.33</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>11.35</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43153</v>
+        <v>43154</v>
       </c>
       <c r="H21" t="n">
-        <v>379.9</v>
+        <v>384.4</v>
       </c>
       <c r="I21" t="n">
         <v>384.2851129946932</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.25</v>
+        <v>-4.47</v>
       </c>
       <c r="L21" t="n">
-        <v>4.93</v>
+        <v>5.1</v>
       </c>
       <c r="M21" t="n">
         <v>1.67</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.05</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43237</v>
+        <v>43238</v>
       </c>
       <c r="H22" t="n">
-        <v>445.5</v>
+        <v>384.9</v>
       </c>
       <c r="I22" t="n">
         <v>440.5928551797863</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K22" t="n">
-        <v>15.89</v>
+        <v>0.13</v>
       </c>
       <c r="L22" t="n">
         <v>7.65</v>
@@ -1695,7 +1958,7 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>4.26</v>
+        <v>13.6</v>
       </c>
       <c r="O22" t="n">
         <v>1.18</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>21.28</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43315</v>
+        <v>43318</v>
       </c>
       <c r="H23" t="n">
-        <v>348.55</v>
+        <v>358.45</v>
       </c>
       <c r="I23" t="n">
         <v>349.1481130441803</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K23" t="n">
-        <v>9.44</v>
+        <v>6.87</v>
       </c>
       <c r="L23" t="n">
         <v>14.6</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.22</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43369</v>
+        <v>43370</v>
       </c>
       <c r="H24" t="n">
-        <v>377.8</v>
+        <v>361.9</v>
       </c>
       <c r="I24" t="n">
         <v>376.4106969904527</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K24" t="n">
-        <v>5.4</v>
+        <v>0.96</v>
       </c>
       <c r="L24" t="n">
         <v>5.97</v>
@@ -1809,7 +2096,7 @@
         <v>0.78</v>
       </c>
       <c r="N24" t="n">
-        <v>3.11</v>
+        <v>4.21</v>
       </c>
       <c r="O24" t="n">
         <v>2.84</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>17.38</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43406</v>
+        <v>43409</v>
       </c>
       <c r="H25" t="n">
-        <v>391.75</v>
+        <v>398.2</v>
       </c>
       <c r="I25" t="n">
         <v>392.0087955987444</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.25</v>
+        <v>-10.03</v>
       </c>
       <c r="L25" t="n">
         <v>13.84</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.48</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43455</v>
+        <v>43458</v>
       </c>
       <c r="H26" t="n">
-        <v>429.85</v>
+        <v>394.45</v>
       </c>
       <c r="I26" t="n">
         <v>414.9478958220446</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K26" t="n">
-        <v>7.95</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>3.19</v>
@@ -1923,7 +2234,7 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.87</v>
+        <v>8.24</v>
       </c>
       <c r="O26" t="n">
         <v>1.65</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>16.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43501</v>
+        <v>43502</v>
       </c>
       <c r="H27" t="n">
-        <v>404.65</v>
+        <v>444.65</v>
       </c>
       <c r="I27" t="n">
         <v>426.4678389746018</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.59</v>
+        <v>-12.73</v>
       </c>
       <c r="L27" t="n">
-        <v>9.609999999999999</v>
+        <v>13.58</v>
       </c>
       <c r="M27" t="n">
         <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2.81</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>-8.24</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>13.76</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43593</v>
+        <v>43594</v>
       </c>
       <c r="H28" t="n">
-        <v>488.9</v>
+        <v>484.75</v>
       </c>
       <c r="I28" t="n">
         <v>485.1255426332838</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K28" t="n">
-        <v>9.949999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="L28" t="n">
         <v>8.42</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>7.83</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43599</v>
+        <v>43600</v>
       </c>
       <c r="H29" t="n">
-        <v>520</v>
+        <v>551.5</v>
       </c>
       <c r="I29" t="n">
         <v>522.6946798304722</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.27</v>
+        <v>-13.77</v>
       </c>
       <c r="L29" t="n">
-        <v>8.32</v>
+        <v>16.14</v>
       </c>
       <c r="M29" t="n">
         <v>1.32</v>
       </c>
       <c r="N29" t="n">
-        <v>5.41</v>
+        <v>6.06</v>
       </c>
       <c r="O29" t="n">
         <v>-0.85</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>12.61</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H30" t="n">
-        <v>576.1</v>
+        <v>559.2</v>
       </c>
       <c r="I30" t="n">
         <v>566.8897475621776</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K30" t="n">
-        <v>4.46</v>
+        <v>1.4</v>
       </c>
       <c r="L30" t="n">
         <v>6.39</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>10.05</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43682</v>
+        <v>43683</v>
       </c>
       <c r="H31" t="n">
-        <v>515.75</v>
+        <v>596.15</v>
       </c>
       <c r="I31" t="n">
         <v>574.5974229846498</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K31" t="n">
-        <v>7.77</v>
+        <v>-6.61</v>
       </c>
       <c r="L31" t="n">
-        <v>3.56</v>
+        <v>9.08</v>
       </c>
       <c r="M31" t="n">
-        <v>0.98</v>
+        <v>2.76</v>
       </c>
       <c r="N31" t="n">
-        <v>3.43</v>
+        <v>15.59</v>
       </c>
       <c r="O31" t="n">
         <v>-2.93</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>17.73</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43749</v>
+        <v>43752</v>
       </c>
       <c r="H32" t="n">
-        <v>538.8</v>
+        <v>522.55</v>
       </c>
       <c r="I32" t="n">
         <v>526.63281814832</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.619999999999999</v>
+        <v>-12.35</v>
       </c>
       <c r="L32" t="n">
-        <v>11.52</v>
+        <v>12.93</v>
       </c>
       <c r="M32" t="n">
         <v>1.79</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.92</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43768</v>
+        <v>43769</v>
       </c>
       <c r="H33" t="n">
-        <v>559.25</v>
+        <v>579.25</v>
       </c>
       <c r="I33" t="n">
         <v>575.4509323984553</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.02</v>
+        <v>-10.85</v>
       </c>
       <c r="L33" t="n">
         <v>12.83</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>12.2</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H34" t="n">
-        <v>828.75</v>
+        <v>778.75</v>
       </c>
       <c r="I34" t="n">
         <v>790.0333139686248</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K34" t="n">
-        <v>43.07</v>
+        <v>34.44</v>
       </c>
       <c r="L34" t="n">
         <v>4.77</v>
       </c>
       <c r="M34" t="n">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="N34" t="n">
-        <v>2.53</v>
+        <v>6.03</v>
       </c>
       <c r="O34" t="n">
         <v>3.58</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.37</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43943</v>
+        <v>43944</v>
       </c>
       <c r="H35" t="n">
-        <v>688.55</v>
+        <v>728.6</v>
       </c>
       <c r="I35" t="n">
         <v>692.8091303996894</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K35" t="n">
-        <v>11.58</v>
+        <v>6.44</v>
       </c>
       <c r="L35" t="n">
         <v>5.27</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>20.11</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44217</v>
+        <v>44218</v>
       </c>
       <c r="H36" t="n">
-        <v>1154.5</v>
+        <v>1081.05</v>
       </c>
       <c r="I36" t="n">
         <v>1099.810813083957</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K36" t="n">
-        <v>58.45</v>
+        <v>48.37</v>
       </c>
       <c r="L36" t="n">
         <v>9.25</v>
@@ -2493,7 +2924,7 @@
         <v>2.09</v>
       </c>
       <c r="N36" t="n">
-        <v>5.04</v>
+        <v>6.36</v>
       </c>
       <c r="O36" t="n">
         <v>5.82</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>191</v>
+        <v>192</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>10</v>
+      </c>
+      <c r="U36" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>14.17</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44286</v>
+        <v>44287</v>
       </c>
       <c r="H37" t="n">
-        <v>1082.15</v>
+        <v>1148.25</v>
       </c>
       <c r="I37" t="n">
         <v>1140.619208803818</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1</v>
+        <v>-6.22</v>
       </c>
       <c r="L37" t="n">
         <v>8.09</v>
@@ -2550,7 +2993,7 @@
         <v>2.2</v>
       </c>
       <c r="N37" t="n">
-        <v>3.44</v>
+        <v>6.11</v>
       </c>
       <c r="O37" t="n">
         <v>-6.36</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.76</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H38" t="n">
-        <v>2307.65</v>
+        <v>2209.1</v>
       </c>
       <c r="I38" t="n">
         <v>2235.015672100002</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K38" t="n">
-        <v>100.97</v>
+        <v>92.39</v>
       </c>
       <c r="L38" t="n">
         <v>5.32</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>7</v>
+      </c>
+      <c r="U38" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>13.45</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44552</v>
+        <v>44553</v>
       </c>
       <c r="H39" t="n">
-        <v>2306</v>
+        <v>2322.45</v>
       </c>
       <c r="I39" t="n">
         <v>2315.92478215598</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.39</v>
+        <v>-5.13</v>
       </c>
       <c r="L39" t="n">
-        <v>5.25</v>
+        <v>5.99</v>
       </c>
       <c r="M39" t="n">
         <v>1.57</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.73</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H40" t="n">
-        <v>2476.8</v>
+        <v>2369.7</v>
       </c>
       <c r="I40" t="n">
         <v>2444.754497667062</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K40" t="n">
-        <v>6.65</v>
+        <v>2.03</v>
       </c>
       <c r="L40" t="n">
         <v>1.35</v>
@@ -2721,7 +3200,7 @@
         <v>1.31</v>
       </c>
       <c r="N40" t="n">
-        <v>3.54</v>
+        <v>4.32</v>
       </c>
       <c r="O40" t="n">
         <v>0.71</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.15</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H41" t="n">
-        <v>2420</v>
+        <v>2469.2</v>
       </c>
       <c r="I41" t="n">
         <v>2450.902736209826</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.12</v>
+        <v>-4.2</v>
       </c>
       <c r="L41" t="n">
         <v>10.22</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.57</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H42" t="n">
-        <v>2489.35</v>
+        <v>2434.75</v>
       </c>
       <c r="I42" t="n">
         <v>2473.048561221569</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K42" t="n">
-        <v>0.82</v>
+        <v>-1.4</v>
       </c>
       <c r="L42" t="n">
         <v>1.95</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.07</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44757</v>
+        <v>44760</v>
       </c>
       <c r="H43" t="n">
-        <v>2261.45</v>
+        <v>2308.5</v>
       </c>
       <c r="I43" t="n">
         <v>2279.997182939633</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K43" t="n">
-        <v>7.12</v>
+        <v>5.19</v>
       </c>
       <c r="L43" t="n">
         <v>4.77</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.08</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H44" t="n">
-        <v>2622.3</v>
+        <v>2572.35</v>
       </c>
       <c r="I44" t="n">
         <v>2578.098401558085</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K44" t="n">
-        <v>13.59</v>
+        <v>11.43</v>
       </c>
       <c r="L44" t="n">
         <v>2.01</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.15</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44966</v>
+        <v>44967</v>
       </c>
       <c r="H45" t="n">
-        <v>2218.35</v>
+        <v>2289.4</v>
       </c>
       <c r="I45" t="n">
         <v>2236.232506431247</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K45" t="n">
-        <v>13.76</v>
+        <v>11</v>
       </c>
       <c r="L45" t="n">
         <v>2.62</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>6</v>
+      </c>
+      <c r="U45" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44984</v>
+        <v>44985</v>
       </c>
       <c r="H46" t="n">
-        <v>2191.9</v>
+        <v>2168.55</v>
       </c>
       <c r="I46" t="n">
         <v>2183.360318000371</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.26</v>
+        <v>-5.28</v>
       </c>
       <c r="L46" t="n">
-        <v>5.59</v>
+        <v>5.91</v>
       </c>
       <c r="M46" t="n">
         <v>0.78</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>7.36</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45005</v>
+        <v>45006</v>
       </c>
       <c r="H47" t="n">
-        <v>2303.35</v>
+        <v>2349.35</v>
       </c>
       <c r="I47" t="n">
         <v>2328.243190823961</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.22</v>
+        <v>-8.34</v>
       </c>
       <c r="L47" t="n">
-        <v>7.65</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>0.71</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.77</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45063</v>
+        <v>45064</v>
       </c>
       <c r="H48" t="n">
-        <v>2471.35</v>
+        <v>2428.6</v>
       </c>
       <c r="I48" t="n">
         <v>2470.530514017769</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K48" t="n">
-        <v>5.19</v>
+        <v>3.37</v>
       </c>
       <c r="L48" t="n">
         <v>2.16</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.32</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45083</v>
+        <v>45084</v>
       </c>
       <c r="H49" t="n">
-        <v>2533.1</v>
+        <v>2567.35</v>
       </c>
       <c r="I49" t="n">
         <v>2566.413755145655</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.3</v>
+        <v>-5.71</v>
       </c>
       <c r="L49" t="n">
-        <v>4.87</v>
+        <v>5.95</v>
       </c>
       <c r="M49" t="n">
         <v>0.75</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.63</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45086</v>
+        <v>45089</v>
       </c>
       <c r="H50" t="n">
-        <v>2429.7</v>
+        <v>2337.85</v>
       </c>
       <c r="I50" t="n">
         <v>2422.884446209235</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.36</v>
+        <v>-8.94</v>
       </c>
       <c r="L50" t="n">
-        <v>5.85</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N50" t="n">
-        <v>3.35</v>
+        <v>3.78</v>
       </c>
       <c r="O50" t="n">
         <v>1.35</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.99</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45146</v>
+        <v>45147</v>
       </c>
       <c r="H51" t="n">
-        <v>2277.95</v>
+        <v>2299.7</v>
       </c>
       <c r="I51" t="n">
         <v>2294.355312504154</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K51" t="n">
-        <v>2.56</v>
+        <v>1.63</v>
       </c>
       <c r="L51" t="n">
         <v>3.72</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.59</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45187</v>
+        <v>45189</v>
       </c>
       <c r="H52" t="n">
-        <v>2368.7</v>
+        <v>2319.85</v>
       </c>
       <c r="I52" t="n">
         <v>2347.213780064735</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>0.88</v>
       </c>
       <c r="L52" t="n">
         <v>1.72</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.65</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H53" t="n">
-        <v>2238.45</v>
+        <v>2253.35</v>
       </c>
       <c r="I53" t="n">
         <v>2251.422420661334</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K53" t="n">
-        <v>3.51</v>
+        <v>2.87</v>
       </c>
       <c r="L53" t="n">
         <v>2.09</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.54</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45299</v>
+        <v>45300</v>
       </c>
       <c r="H54" t="n">
-        <v>2395.7</v>
+        <v>2311.35</v>
       </c>
       <c r="I54" t="n">
         <v>2346.704530750279</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K54" t="n">
-        <v>6.32</v>
+        <v>2.57</v>
       </c>
       <c r="L54" t="n">
         <v>0.78</v>
@@ -3519,7 +4166,7 @@
         <v>0.51</v>
       </c>
       <c r="N54" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="O54" t="n">
         <v>0.67</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.49</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45342</v>
+        <v>45343</v>
       </c>
       <c r="H55" t="n">
-        <v>2383.2</v>
+        <v>2398.95</v>
       </c>
       <c r="I55" t="n">
         <v>2389.111364416779</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.11</v>
+        <v>-3.79</v>
       </c>
       <c r="L55" t="n">
-        <v>4.73</v>
+        <v>4.85</v>
       </c>
       <c r="M55" t="n">
         <v>0.91</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.13</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45418</v>
+        <v>45419</v>
       </c>
       <c r="H56" t="n">
-        <v>2587.6</v>
+        <v>2416.85</v>
       </c>
       <c r="I56" t="n">
         <v>2476.5067959369</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K56" t="n">
-        <v>7.86</v>
+        <v>0.75</v>
       </c>
       <c r="L56" t="n">
         <v>2.38</v>
@@ -3633,7 +4304,7 @@
         <v>1.99</v>
       </c>
       <c r="N56" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="O56" t="n">
         <v>0.66</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>11.99</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="H57" t="n">
-        <v>2365.9</v>
+        <v>2399.9</v>
       </c>
       <c r="I57" t="n">
         <v>2368.161534108606</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K57" t="n">
-        <v>2.11</v>
+        <v>0.7</v>
       </c>
       <c r="L57" t="n">
         <v>5.1</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.33</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45548</v>
+        <v>45551</v>
       </c>
       <c r="H58" t="n">
-        <v>2466.4</v>
+        <v>2436.9</v>
       </c>
       <c r="I58" t="n">
         <v>2451.746925921119</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K58" t="n">
-        <v>2.77</v>
+        <v>1.54</v>
       </c>
       <c r="L58" t="n">
         <v>4.87</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.7</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="H59" t="n">
-        <v>2302.35</v>
+        <v>2343.6</v>
       </c>
       <c r="I59" t="n">
         <v>2338.314041696546</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K59" t="n">
-        <v>5.52</v>
+        <v>3.83</v>
       </c>
       <c r="L59" t="n">
         <v>3.41</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>7.5</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H60" t="n">
-        <v>2854.85</v>
+        <v>2715.2</v>
       </c>
       <c r="I60" t="n">
         <v>2804.95169084662</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K60" t="n">
-        <v>21.81</v>
+        <v>15.86</v>
       </c>
       <c r="L60" t="n">
         <v>6.26</v>
       </c>
       <c r="M60" t="n">
-        <v>5.49</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="N60" t="n">
-        <v>3.27</v>
+        <v>4.89</v>
       </c>
       <c r="O60" t="n">
         <v>1.79</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>11.05</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H61" t="n">
-        <v>2990.4</v>
+        <v>3029.3</v>
       </c>
       <c r="I61" t="n">
         <v>3015.278235068951</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.14</v>
+        <v>-11.57</v>
       </c>
       <c r="L61" t="n">
-        <v>11.41</v>
+        <v>12.11</v>
       </c>
       <c r="M61" t="n">
         <v>3.44</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.46</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H62" t="n">
-        <v>3150.4</v>
+        <v>3040.8</v>
       </c>
       <c r="I62" t="n">
         <v>3080.682255032415</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K62" t="n">
-        <v>4</v>
+        <v>0.38</v>
       </c>
       <c r="L62" t="n">
         <v>6.94</v>
@@ -3975,7 +4718,7 @@
         <v>2.47</v>
       </c>
       <c r="N62" t="n">
-        <v>3.37</v>
+        <v>3.48</v>
       </c>
       <c r="O62" t="n">
         <v>1.3</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.69</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="H63" t="n">
-        <v>2972.7</v>
+        <v>2996.9</v>
       </c>
       <c r="I63" t="n">
         <v>2982.673268022045</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K63" t="n">
-        <v>2.24</v>
+        <v>1.44</v>
       </c>
       <c r="L63" t="n">
         <v>3.39</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.73</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="H64" t="n">
-        <v>3027.8</v>
+        <v>2981.1</v>
       </c>
       <c r="I64" t="n">
         <v>3007.301889652138</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K64" t="n">
-        <v>1.03</v>
+        <v>-0.53</v>
       </c>
       <c r="L64" t="n">
-        <v>0.66</v>
+        <v>1.16</v>
       </c>
       <c r="M64" t="n">
         <v>0.61</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.73</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="H65" t="n">
-        <v>2943.7</v>
+        <v>3023.6</v>
       </c>
       <c r="I65" t="n">
         <v>2975.890741713903</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K65" t="n">
-        <v>1.25</v>
+        <v>-1.43</v>
       </c>
       <c r="L65" t="n">
         <v>1.74</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>7.82</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H66" t="n">
-        <v>2962.5</v>
+        <v>2883.2</v>
       </c>
       <c r="I66" t="n">
         <v>2946.158863023114</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.02</v>
+        <v>-4.64</v>
       </c>
       <c r="L66" t="n">
-        <v>3.06</v>
+        <v>6.3</v>
       </c>
       <c r="M66" t="n">
         <v>1.2</v>
       </c>
       <c r="N66" t="n">
-        <v>2.14</v>
+        <v>2.68</v>
       </c>
       <c r="O66" t="n">
         <v>2.71</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.32</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H67" t="n">
-        <v>2901.6</v>
+        <v>2986.7</v>
       </c>
       <c r="I67" t="n">
         <v>2941.513864669886</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.64</v>
+        <v>-3.59</v>
       </c>
       <c r="L67" t="n">
         <v>6.88</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>10.67</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="H68" t="n">
-        <v>2730.4</v>
+        <v>2678.7</v>
       </c>
       <c r="I68" t="n">
         <v>2701.34651202309</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>-8.58</v>
+        <v>-10.31</v>
       </c>
       <c r="L68" t="n">
-        <v>9.74</v>
+        <v>10.81</v>
       </c>
       <c r="M68" t="n">
         <v>1.2</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>10.87</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H69" t="n">
-        <v>2522.8</v>
+        <v>2719.6</v>
       </c>
       <c r="I69" t="n">
         <v>2686.750739660793</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K69" t="n">
-        <v>5.82</v>
+        <v>-1.53</v>
       </c>
       <c r="L69" t="n">
-        <v>2.33</v>
+        <v>3.11</v>
       </c>
       <c r="M69" t="n">
         <v>4.34</v>
       </c>
       <c r="N69" t="n">
-        <v>5.53</v>
+        <v>7.8</v>
       </c>
       <c r="O69" t="n">
         <v>-1.89</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>11.22</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H70" t="n">
-        <v>2867.2</v>
+        <v>2622.7</v>
       </c>
       <c r="I70" t="n">
         <v>2698.693672471941</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K70" t="n">
-        <v>5.43</v>
+        <v>-3.56</v>
       </c>
       <c r="L70" t="n">
         <v>5.05</v>
@@ -4431,7 +5270,7 @@
         <v>2.14</v>
       </c>
       <c r="N70" t="n">
-        <v>3.6</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="O70" t="n">
         <v>7.8</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>67</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101.4</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.6</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.79</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.42</v>
+        <v>-3.31</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100.97</v>
+        <v>92.39</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62.3</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.73</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.27</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="21">
@@ -9609,7 +10468,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.6</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="22">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="25">
@@ -9649,7 +10508,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.619999999999999</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.06</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="27">
@@ -9669,7 +10528,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.539999999999999</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="28">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
